--- a/dist/downloads/model-documents/kimi-kimi-audio-7b.xlsx
+++ b/dist/downloads/model-documents/kimi-kimi-audio-7b.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R9a916633aa5643e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="R0a5379bba8a34229"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="算子表" sheetId="1" r:id="R3a9f6e81e3cc42bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模型参数" sheetId="2" r:id="Rff0f931774ee4da2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1061,7 +1061,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD6" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
@@ -2257,7 +2257,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD19" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" hidden="0" customHeight="1">
@@ -3453,7 +3453,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD32" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="24" hidden="0" customHeight="1">
@@ -4649,7 +4649,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD45" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="24" hidden="0" customHeight="1">
@@ -5845,7 +5845,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD58" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="24" hidden="0" customHeight="1">
@@ -7041,7 +7041,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD71" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="24" hidden="0" customHeight="1">
@@ -8237,7 +8237,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD84" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="24" hidden="0" customHeight="1">
@@ -9433,7 +9433,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD97" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="24" hidden="0" customHeight="1">
@@ -10629,7 +10629,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD110" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="24" hidden="0" customHeight="1">
@@ -11825,7 +11825,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD123" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="24" hidden="0" customHeight="1">
@@ -13021,7 +13021,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD136" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="24" hidden="0" customHeight="1">
@@ -14217,7 +14217,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD149" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="24" hidden="0" customHeight="1">
@@ -15413,7 +15413,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD162" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="24" hidden="0" customHeight="1">
@@ -16609,7 +16609,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD175" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="24" hidden="0" customHeight="1">
@@ -17805,7 +17805,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD188" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="24" hidden="0" customHeight="1">
@@ -19001,7 +19001,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD201" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="24" hidden="0" customHeight="1">
@@ -20197,7 +20197,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD214" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="24" hidden="0" customHeight="1">
@@ -21393,7 +21393,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD227" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="24" hidden="0" customHeight="1">
@@ -22589,7 +22589,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD240" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="24" hidden="0" customHeight="1">
@@ -23785,7 +23785,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD253" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="24" hidden="0" customHeight="1">
@@ -24981,7 +24981,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD266" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="24" hidden="0" customHeight="1">
@@ -26177,7 +26177,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD279" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="24" hidden="0" customHeight="1">
@@ -27373,7 +27373,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD292" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="24" hidden="0" customHeight="1">
@@ -28569,7 +28569,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD305" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="24" hidden="0" customHeight="1">
@@ -29765,7 +29765,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD318" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="24" hidden="0" customHeight="1">
@@ -30961,7 +30961,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD331" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="24" hidden="0" customHeight="1">
@@ -32157,7 +32157,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD344" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="24" hidden="0" customHeight="1">
@@ -33353,7 +33353,7 @@
         <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；</x:v>
       </x:c>
       <x:c r="AD357" s="12" t="str">
-        <x:v>cache长度L_KV独立；位置编码类型与存储layout未核验</x:v>
+        <x:v>文本decode/verify；B[1,16],S[1,8]；TP=1逻辑参考；位置编码与物理layout需实现核验</x:v>
       </x:c>
     </x:row>
     <x:row r="358" ht="24" hidden="0" customHeight="1">
@@ -34106,16 +34106,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E366" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F366" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G366" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H366" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I366" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34178,7 +34178,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC366" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD366" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -34198,16 +34198,16 @@
         <x:v>专用状态/混合注意力</x:v>
       </x:c>
       <x:c r="E367" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]; state=未知</x:v>
+        <x:v>[B,L_audio,H_unknown]; state=未知</x:v>
       </x:c>
       <x:c r="F367" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G367" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H367" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I367" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34270,7 +34270,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC367" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD367" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -34290,16 +34290,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E368" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F368" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G368" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H368" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I368" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34362,7 +34362,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC368" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD368" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -34382,16 +34382,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E369" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F369" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G369" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H369" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I369" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34454,7 +34454,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC369" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD369" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -34474,16 +34474,16 @@
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="E370" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F370" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G370" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H370" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I370" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34546,7 +34546,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC370" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD370" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -34566,16 +34566,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E371" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F371" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G371" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H371" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I371" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34638,7 +34638,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC371" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD371" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -34658,16 +34658,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E372" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F372" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G372" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H372" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I372" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34730,7 +34730,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC372" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD372" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -34750,16 +34750,16 @@
         <x:v>专用状态/混合注意力</x:v>
       </x:c>
       <x:c r="E373" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]; state=未知</x:v>
+        <x:v>[B,L_audio,H_unknown]; state=未知</x:v>
       </x:c>
       <x:c r="F373" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G373" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H373" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I373" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34822,7 +34822,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC373" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD373" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -34842,16 +34842,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E374" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F374" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G374" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H374" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I374" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -34914,7 +34914,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC374" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD374" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -34934,16 +34934,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E375" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F375" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G375" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H375" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I375" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35006,7 +35006,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC375" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD375" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -35026,16 +35026,16 @@
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="E376" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F376" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G376" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H376" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I376" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35098,7 +35098,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC376" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD376" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -35118,16 +35118,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E377" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F377" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G377" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H377" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I377" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35190,7 +35190,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC377" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD377" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -35210,16 +35210,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E378" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F378" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G378" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H378" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I378" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35282,7 +35282,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC378" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD378" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -35302,16 +35302,16 @@
         <x:v>专用状态/混合注意力</x:v>
       </x:c>
       <x:c r="E379" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]; state=未知</x:v>
+        <x:v>[B,L_audio,H_unknown]; state=未知</x:v>
       </x:c>
       <x:c r="F379" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G379" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H379" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I379" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35374,7 +35374,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC379" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD379" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -35394,16 +35394,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E380" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F380" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G380" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H380" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I380" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35466,7 +35466,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC380" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD380" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -35486,16 +35486,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E381" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F381" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G381" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H381" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I381" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35558,7 +35558,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC381" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD381" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -35578,16 +35578,16 @@
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="E382" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F382" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G382" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H382" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I382" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35650,7 +35650,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC382" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD382" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -35670,16 +35670,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E383" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F383" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G383" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H383" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I383" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35742,7 +35742,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC383" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD383" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -35762,16 +35762,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E384" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F384" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G384" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H384" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I384" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35834,7 +35834,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC384" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD384" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -35854,16 +35854,16 @@
         <x:v>专用状态/混合注意力</x:v>
       </x:c>
       <x:c r="E385" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]; state=未知</x:v>
+        <x:v>[B,L_audio,H_unknown]; state=未知</x:v>
       </x:c>
       <x:c r="F385" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G385" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H385" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I385" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -35926,7 +35926,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC385" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD385" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -35946,16 +35946,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E386" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F386" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G386" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H386" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I386" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36018,7 +36018,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC386" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD386" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36038,16 +36038,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E387" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F387" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G387" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H387" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I387" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36110,7 +36110,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC387" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD387" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -36130,16 +36130,16 @@
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="E388" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F388" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G388" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H388" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I388" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36202,7 +36202,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC388" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD388" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -36222,16 +36222,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E389" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F389" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G389" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H389" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I389" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36294,7 +36294,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC389" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD389" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36314,16 +36314,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E390" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F390" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G390" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H390" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I390" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36386,7 +36386,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC390" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD390" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -36406,16 +36406,16 @@
         <x:v>专用状态/混合注意力</x:v>
       </x:c>
       <x:c r="E391" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]; state=未知</x:v>
+        <x:v>[B,L_audio,H_unknown]; state=未知</x:v>
       </x:c>
       <x:c r="F391" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G391" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H391" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I391" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36478,7 +36478,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC391" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD391" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -36498,16 +36498,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E392" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F392" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G392" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H392" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I392" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36570,7 +36570,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC392" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD392" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36590,16 +36590,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E393" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F393" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G393" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H393" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I393" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36662,7 +36662,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC393" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD393" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -36682,16 +36682,16 @@
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="E394" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F394" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G394" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H394" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I394" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36754,7 +36754,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC394" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD394" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -36774,16 +36774,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E395" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F395" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G395" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H395" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I395" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36846,7 +36846,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC395" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD395" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -36866,16 +36866,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E396" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F396" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G396" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H396" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I396" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -36938,7 +36938,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC396" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD396" s="12" t="str">
         <x:v>归一化类型/先后顺序待实现核验</x:v>
@@ -36958,16 +36958,16 @@
         <x:v>专用状态/混合注意力</x:v>
       </x:c>
       <x:c r="E397" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]; state=未知</x:v>
+        <x:v>[B,L_audio,H_unknown]; state=未知</x:v>
       </x:c>
       <x:c r="F397" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G397" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H397" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I397" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37030,7 +37030,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC397" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；不将标准full attention套入专用递归结构</x:v>
       </x:c>
       <x:c r="AD397" s="12" t="str">
         <x:v>配置确认层类型与外部宽度；内部Q/K/V/门控/状态需要固定源码</x:v>
@@ -37050,16 +37050,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E398" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F398" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G398" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H398" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I398" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37122,7 +37122,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC398" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD398" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -37142,16 +37142,16 @@
         <x:v>norm</x:v>
       </x:c>
       <x:c r="E399" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F399" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G399" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H399" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I399" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37214,7 +37214,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC399" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD399" s="12" t="str">
         <x:v>类型与位置待源码核验</x:v>
@@ -37234,16 +37234,16 @@
         <x:v>未核验</x:v>
       </x:c>
       <x:c r="E400" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F400" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G400" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H400" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I400" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37306,7 +37306,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC400" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD400" s="12" t="str">
         <x:v>专用结构或配置缺FFN宽度，保留缺口</x:v>
@@ -37326,16 +37326,16 @@
         <x:v>elementwise</x:v>
       </x:c>
       <x:c r="E401" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown];[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown];[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="F401" s="12" t="str">
-        <x:v>[B,L_mod,H_unknown]</x:v>
+        <x:v>[B,L_audio,H_unknown]</x:v>
       </x:c>
       <x:c r="G401" s="12" t="str">
-        <x:v>B,S,T；其他轴见模型参数</x:v>
+        <x:v>B,L_audio；模态独立长度</x:v>
       </x:c>
       <x:c r="H401" s="12" t="str">
-        <x:v>B[1,16];S_verify[1,8];L_KV独立未知；TP=1</x:v>
+        <x:v>L_audio由模态输入/输出决定；不是S_verify</x:v>
       </x:c>
       <x:c r="I401" s="12" t="str">
         <x:v>config=bfloat16；激活/累加类型未核验</x:v>
@@ -37398,7 +37398,7 @@
         <x:v>https://huggingface.co/moonshotai/Kimi-Audio-7B/resolve/d90be7113cd5be6bcf54fae2aabcad060a23f6cf/config.json</x:v>
       </x:c>
       <x:c r="AC401" s="12" t="str">
-        <x:v>专用模态阶段；S_verify不替代模态序列长度；</x:v>
+        <x:v>专用模态阶段；长度/缓存需源码，S_verify不替代模态序列长度；</x:v>
       </x:c>
       <x:c r="AD401" s="12" t="str">
         <x:v>Y=X+branch（参考，实际残差策略未核验）</x:v>
@@ -37651,7 +37651,7 @@
         </x:is>
       </x:c>
       <x:c r="C7" s="28" t="n">
-        <x:f>IF(ISNUMBER(C6),IF(AND(C20&gt;=1,MOD(C6,C20)=0),C6/C20,"未核验"),"未核验")</x:f>
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,IF(ISNUMBER(C6),IF(MOD(C6,C20)=0,C6/C20,"未核验"),"未核验"),"未核验"),"未核验"),"未核验")</x:f>
         <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="28" t="str">
@@ -37915,7 +37915,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="28"/>
-      <x:c r="E20" s="28"/>
+      <x:c r="E20" s="28" t="str">
+        <x:f>IF(ISNUMBER(C20),IF(C20&gt;=1,IF(MOD(C20,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="28" t="str">
@@ -37928,7 +37931,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="28"/>
-      <x:c r="E21" s="28"/>
+      <x:c r="E21" s="28" t="str">
+        <x:f>IF(ISNUMBER(C21),IF(C21&gt;=1,IF(MOD(C21,1)=0,"正整数场景输入；实际支持未核验","须为正整数"),"须为正整数"),"须为正整数")</x:f>
+        <x:v>正整数场景输入；实际支持未核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="28" t="str">
@@ -38518,8 +38524,8 @@
       <x:c r="E68" s="28"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="whole" operator="between" sqref="C3:C4">
+  <x:dataValidations count="3">
+    <x:dataValidation type="whole" operator="between" sqref="C3">
       <x:formula1>1</x:formula1>
       <x:formula2>16</x:formula2>
     </x:dataValidation>
@@ -38527,6 +38533,9 @@
       <x:formula1>1</x:formula1>
       <x:formula2>8</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" sqref="C20:C21">
+      <x:formula1>1</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
